--- a/Base_de_donnees/Fichiers_metadonnees/Metadonnees_localisations.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/Metadonnees_localisations.xlsx
@@ -58,103 +58,103 @@
     <t xml:space="preserve">description_milieu</t>
   </si>
   <si>
-    <t xml:space="preserve">HOBO_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOBO_38</t>
+    <t xml:space="preserve">HOBO_n°01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOBO_n°38</t>
   </si>
   <si>
     <t xml:space="preserve">id_milieu_spécifique  (si utilisé ailleurs)</t>
@@ -319,7 +319,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -327,15 +327,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -532,8 +532,8 @@
   <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.95"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="21.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="33.94"/>
@@ -575,7 +575,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="5" t="n">
@@ -594,7 +594,7 @@
       <c r="K2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="5" t="n">
@@ -611,7 +611,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="5" t="n">
@@ -626,7 +626,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="5" t="n">
@@ -640,7 +640,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="5" t="n">
@@ -654,7 +654,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="5" t="n">
@@ -668,7 +668,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="5" t="n">
@@ -682,7 +682,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="5" t="n">
@@ -696,7 +696,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="5" t="n">
@@ -710,7 +710,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="5" t="n">
@@ -724,7 +724,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B12" s="5" t="n">
@@ -738,7 +738,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B13" s="5" t="n">
@@ -752,7 +752,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="5" t="n">
@@ -766,7 +766,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="5" t="n">
@@ -780,7 +780,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B16" s="5" t="n">
@@ -794,7 +794,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B17" s="5" t="n">
@@ -808,7 +808,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="5" t="n">
@@ -822,7 +822,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="5" t="n">
@@ -836,7 +836,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="5" t="n">
@@ -850,7 +850,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B21" s="5" t="n">
@@ -864,7 +864,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B22" s="5" t="n">
@@ -878,7 +878,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="5" t="n">
@@ -892,7 +892,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B24" s="5" t="n">
@@ -906,7 +906,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B25" s="5" t="n">
@@ -920,7 +920,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B26" s="5" t="n">
@@ -934,7 +934,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B27" s="5" t="n">
@@ -948,7 +948,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B28" s="5" t="n">
@@ -962,7 +962,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B29" s="5" t="n">
@@ -981,7 +981,7 @@
       <c r="F30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B31" s="5" t="n">
@@ -995,7 +995,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B32" s="5" t="n">
@@ -1014,7 +1014,7 @@
       <c r="F33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B34" s="5" t="n">
@@ -1038,7 +1038,7 @@
       <c r="F36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B37" s="5" t="n">
@@ -1057,7 +1057,7 @@
       <c r="F38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B39" s="5" t="n">

--- a/Base_de_donnees/Fichiers_metadonnees/Metadonnees_localisations.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/Metadonnees_localisations.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t xml:space="preserve">identifiant_instrument (num_instrument)</t>
   </si>
@@ -155,6 +155,15 @@
   </si>
   <si>
     <t xml:space="preserve">HOBO_n°38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMS4_n°0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dendro_n°0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">id_milieu_spécifique  (si utilisé ailleurs)</t>
@@ -183,7 +192,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -255,6 +264,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -298,7 +314,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -337,6 +353,10 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -526,11 +546,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.95"/>
@@ -1068,6 +1087,34 @@
       </c>
       <c r="F39" s="8" t="n">
         <v>43.6321227</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>45170</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1084,11 +1131,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.38"/>
@@ -1096,13 +1142,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D1" s="2"/>
     </row>
@@ -1120,24 +1166,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D1" s="2"/>
     </row>
@@ -1155,18 +1200,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C1" s="2"/>
     </row>

--- a/Base_de_donnees/Fichiers_metadonnees/Metadonnees_localisations.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/Metadonnees_localisations.xlsx
@@ -157,10 +157,10 @@
     <t xml:space="preserve">HOBO_n°38</t>
   </si>
   <si>
-    <t xml:space="preserve">TMS4_n°0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dendro_n°0</t>
+    <t xml:space="preserve">TMS4_95224601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dendro_92261195</t>
   </si>
   <si>
     <t xml:space="preserve">01/03/2026</t>
@@ -192,7 +192,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -265,6 +265,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos"/>
@@ -314,7 +320,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -356,6 +362,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1090,7 +1100,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="10" t="s">
         <v>44</v>
       </c>
       <c r="B40" s="5" t="n">
@@ -1104,16 +1114,16 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E41" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="0" t="n">
+      <c r="F41" s="1" t="n">
         <v>0</v>
       </c>
     </row>
